--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0101.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0101.xlsx
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Ủa, ngươi muốn chơi kiểu này hả? Kéo tay ta để phá thế à?</t>
+          <t>Ủa, mày muốn chơi kiểu này hả? Kéo tay tao để phá thế à?</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Lúc nãy cậu làm ta giật cả mình! Giờ coi như hòa nhé!</t>
+          <t>Lúc nãy cậu làm tao giật cả mình! Giờ coi như hòa nhé!</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Còn đối với các Cộng Hưởng Giả bình thường, họ cũng có thể ngăn ngừa tình trạng Quá Tải đấy!</t>
+          <t>Còn đối với các Resonator bình thường, họ cũng có thể ngăn ngừa tình trạng Quá Tải đấy!</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chết tiệt. Được rồi, ta làm, nhưng chỉ vì chúng ta là bạn thôi!</t>
+          <t>Chết tiệt. Được rồi, tao làm, nhưng chỉ vì chúng ta là bạn thôi!</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Trong khi tụi bay phí thời gian ở chỗ sai, ta sẽ tự mình lấy giải thưởng!</t>
+          <t>Trong khi tụi bay phí thời gian ở chỗ sai, tao sẽ tự mình lấy giải thưởng!</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Nhìn đống báo cáo ta phải nộp này! Hay là ta hoa mắt vì mì ly Agronomy Wing kỳ cục kia chứ?</t>
+          <t>Nhìn đống báo cáo tao phải nộp này! Hay là tao hoa mắt vì mì ly Agronomy Wing kỳ cục kia chứ?</t>
         </is>
       </c>
     </row>
